--- a/portal-supervisao-360/src/assets/modelo.xlsx
+++ b/portal-supervisao-360/src/assets/modelo.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/2-SSD EXT 1T/2-BDHelix-TFS/app-supervisao-360/Cargas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruno.menezes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADE6460-6CA8-B44F-9209-CF7473463095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="600" windowWidth="27840" windowHeight="16220" xr2:uid="{80DF40C6-15B1-B947-AACB-CFA34DA7D4F6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="13620"/>
   </bookViews>
   <sheets>
-    <sheet name="Profissionais" sheetId="1" r:id="rId1"/>
-    <sheet name="Clientes" sheetId="3" r:id="rId2"/>
+    <sheet name="Tabelao" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,12 +35,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{0D0E5364-77F2-A94A-9675-97BA588FAADE}">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -80,10 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
-  <si>
-    <t>CodVendedor</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Email</t>
   </si>
@@ -119,13 +114,31 @@
   </si>
   <si>
     <t>CodSuperior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">teste empresa </t>
+  </si>
+  <si>
+    <t>22.055.198/0001-43</t>
+  </si>
+  <si>
+    <t>teste@email.com</t>
+  </si>
+  <si>
+    <t>teste</t>
+  </si>
+  <si>
+    <t>(15) 99999-9999</t>
+  </si>
+  <si>
+    <t>sim</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -153,6 +166,22 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -171,17 +200,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -513,96 +546,119 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D533851A-271C-744D-A032-B5081FD59352}">
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:V5"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" s="2" customFormat="1" ht="15.75">
       <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>123</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>123</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2">
+        <v>123</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="L5" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E143370B-E005-CC41-8275-B6B2A6974C63}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="5.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/portal-supervisao-360/src/assets/modelo.xlsx
+++ b/portal-supervisao-360/src/assets/modelo.xlsx
@@ -1,40 +1,42 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruno.menezes\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="13620"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Tabelao" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Planilhas</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>Tabelao</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <Company/>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>Roberto Okada</dc:creator>
+  <cp:lastModifiedBy>Bruno Menezes - LiveFacilities</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-04-20T17:56:34Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-04-28T21:32:27Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Microsoft Office User</author>
@@ -77,8 +79,8 @@
 </comments>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="21">
   <si>
     <t>Email</t>
   </si>
@@ -132,11 +134,20 @@
   </si>
   <si>
     <t>sim</t>
+  </si>
+  <si>
+    <t>SupNome</t>
+  </si>
+  <si>
+    <t>SupEmail</t>
+  </si>
+  <si>
+    <t>SupCelular</t>
   </si>
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6">
     <font>
@@ -230,7 +241,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -545,7 +556,42 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruno.menezes\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="13620"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Tabelao" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V5"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
@@ -594,23 +640,27 @@
         <v>2</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="V1" s="1"/>
+      <c r="U1" s="1"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2">
@@ -637,21 +687,18 @@
       <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2">
+        <v>123</v>
+      </c>
+      <c r="J2" t="s">
         <v>17</v>
       </c>
-      <c r="J2">
-        <v>123</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2">
+      <c r="K2">
         <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:22">
-      <c r="L5" s="4"/>
+      <c r="K5" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
